--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136645984</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136647156</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136647195</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136647289</v>
       </c>
       <c r="B16" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136645664</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>136645922</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>136647260</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>136647382</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136647450</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136647460</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136645471</v>
       </c>
       <c r="B23" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136647402</v>
       </c>
       <c r="B24" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136645984</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136647156</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136647195</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136647289</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136645664</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>136645922</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>136647260</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>136647382</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136647450</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136647460</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136645471</v>
       </c>
       <c r="B23" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136647402</v>
       </c>
       <c r="B24" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24674-2026 artfynd.xlsx
+++ b/artfynd/A 24674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136645969</v>
       </c>
       <c r="B2" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136645984</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136647156</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136647195</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136645372</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136645539</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136645854</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136645905</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136645934</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136647229</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136647253</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136647356</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136647427</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136647442</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136647289</v>
       </c>
       <c r="B16" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136645664</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>136645922</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>136647260</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>136647382</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136647450</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136647460</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136645471</v>
       </c>
       <c r="B23" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136647402</v>
       </c>
       <c r="B24" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
